--- a/Dados/tablePOP_1.xlsx
+++ b/Dados/tablePOP_1.xlsx
@@ -1,21 +1,71 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rsgovbr-my.sharepoint.com/personal/fernanda-silva_spgg_rs_gov_br1/Documents/Projetos/PNAD/PNAD_projetos/Dados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_4321FFCA8F79A8D366075C52F37BD272DACA0B10" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCE96BDD-0FA9-4BE8-84E6-CFC0D71A3E92}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="13">
+  <si>
+    <t>trabalho_id</t>
+  </si>
+  <si>
+    <t>ocuapacao_id</t>
+  </si>
+  <si>
+    <t>freq_1030</t>
+  </si>
+  <si>
+    <t>freq_1030_cv</t>
+  </si>
+  <si>
+    <t>freq_1034</t>
+  </si>
+  <si>
+    <t>freq_1034_cv</t>
+  </si>
+  <si>
+    <t>ano</t>
+  </si>
+  <si>
+    <t>Dentro</t>
+  </si>
+  <si>
+    <t>Desocupadas</t>
+  </si>
+  <si>
+    <t>Ocupada</t>
+  </si>
+  <si>
+    <t>Fora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uf </t>
+  </si>
+  <si>
+    <t>pop</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +113,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +165,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +199,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +234,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,1030 +410,901 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>trabalho_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ocuapacao_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>freq_1030</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>freq_1030_cv</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>freq_1034</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>freq_1034_cv</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>54168783107711.49</v>
+        <v>54168783107711.492</v>
       </c>
       <c r="D2">
-        <v>0.01958765910007869</v>
+        <v>1.9587659100078689E-2</v>
       </c>
       <c r="E2">
-        <v>58877738445673.7</v>
+        <v>58877738445673.703</v>
       </c>
       <c r="F2">
-        <v>0.01141195370031261</v>
+        <v>1.1411953700312611E-2</v>
       </c>
       <c r="G2">
         <v>2012</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
       </c>
       <c r="C3">
         <v>708340611636712.5</v>
       </c>
       <c r="D3">
-        <v>0.003716077603797235</v>
+        <v>3.7160776037972348E-3</v>
       </c>
       <c r="E3">
-        <v>644189376105275.8</v>
+        <v>644189376105275.75</v>
       </c>
       <c r="F3">
-        <v>0.002119058383250731</v>
+        <v>2.1190583832507311E-3</v>
       </c>
       <c r="G3">
         <v>2012</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>443034627466598.3</v>
+        <v>443034627466598.31</v>
       </c>
       <c r="D4">
-        <v>0.005869747867527172</v>
+        <v>5.8697478675271723E-3</v>
       </c>
       <c r="E4">
-        <v>366801510319810.1</v>
+        <v>366801510319810.13</v>
       </c>
       <c r="F4">
-        <v>0.003605222890040207</v>
+        <v>3.6052228900402068E-3</v>
       </c>
       <c r="G4">
         <v>2012</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>55112889151334.61</v>
+        <v>55112889151334.609</v>
       </c>
       <c r="D5">
-        <v>0.02067994586684046</v>
+        <v>2.0679945866840459E-2</v>
       </c>
       <c r="E5">
-        <v>59196044737016.34</v>
+        <v>59196044737016.344</v>
       </c>
       <c r="F5">
-        <v>0.01229036362097582</v>
+        <v>1.229036362097582E-2</v>
       </c>
       <c r="G5">
         <v>2013</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>724686760701547.6</v>
+        <v>724686760701547.63</v>
       </c>
       <c r="D6">
-        <v>0.003286233063082938</v>
+        <v>3.2862330630829381E-3</v>
       </c>
       <c r="E6">
         <v>658631712557705.5</v>
       </c>
       <c r="F6">
-        <v>0.002014677409660877</v>
+        <v>2.0146774096608771E-3</v>
       </c>
       <c r="G6">
         <v>2013</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
       </c>
       <c r="C7">
         <v>450317218006216.5</v>
       </c>
       <c r="D7">
-        <v>0.005881842504718484</v>
+        <v>5.881842504718484E-3</v>
       </c>
       <c r="E7">
         <v>371219750069137.5</v>
       </c>
       <c r="F7">
-        <v>0.003702051815556183</v>
+        <v>3.702051815556183E-3</v>
       </c>
       <c r="G7">
         <v>2013</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>53725722339888.4</v>
+        <v>53725722339888.398</v>
       </c>
       <c r="D8">
-        <v>0.02153021047658286</v>
+        <v>2.1530210476582861E-2</v>
       </c>
       <c r="E8">
-        <v>57226915717097.51</v>
+        <v>57226915717097.508</v>
       </c>
       <c r="F8">
-        <v>0.01351850458825207</v>
+        <v>1.3518504588252069E-2</v>
       </c>
       <c r="G8">
         <v>2014</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>736780216393415.1</v>
+        <v>736780216393415.13</v>
       </c>
       <c r="D9">
-        <v>0.004217155578135803</v>
+        <v>4.2171555781358033E-3</v>
       </c>
       <c r="E9">
-        <v>667801991736982.6</v>
+        <v>667801991736982.63</v>
       </c>
       <c r="F9">
-        <v>0.00212312535263352</v>
+        <v>2.1231253526335201E-3</v>
       </c>
       <c r="G9">
         <v>2014</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>465816148794214.8</v>
+        <v>465816148794214.81</v>
       </c>
       <c r="D10">
-        <v>0.006719887176802466</v>
+        <v>6.7198871768024658E-3</v>
       </c>
       <c r="E10">
         <v>382388808686571</v>
       </c>
       <c r="F10">
-        <v>0.003708209507915823</v>
+        <v>3.7082095079158232E-3</v>
       </c>
       <c r="G10">
         <v>2014</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>72924023477817.14</v>
+        <v>72924023477817.141</v>
       </c>
       <c r="D11">
-        <v>0.02145194583873992</v>
+        <v>2.1451945838739921E-2</v>
       </c>
       <c r="E11">
-        <v>73722491462048.31</v>
+        <v>73722491462048.313</v>
       </c>
       <c r="F11">
-        <v>0.01274732833201072</v>
+        <v>1.274732833201072E-2</v>
       </c>
       <c r="G11">
         <v>2015</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>741654899109574.3</v>
+        <v>741654899109574.25</v>
       </c>
       <c r="D12">
-        <v>0.00365152281129563</v>
+        <v>3.65152281129563E-3</v>
       </c>
       <c r="E12">
-        <v>669858632799690.8</v>
+        <v>669858632799690.75</v>
       </c>
       <c r="F12">
-        <v>0.00200853030442389</v>
+        <v>2.0085303044238899E-3</v>
       </c>
       <c r="G12">
         <v>2015</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
       </c>
       <c r="C13">
-        <v>463897037865070.7</v>
+        <v>463897037865070.69</v>
       </c>
       <c r="D13">
-        <v>0.006480875030600125</v>
+        <v>6.4808750306001254E-3</v>
       </c>
       <c r="E13">
-        <v>380130105921174.4</v>
+        <v>380130105921174.38</v>
       </c>
       <c r="F13">
-        <v>0.003347978581035257</v>
+        <v>3.347978581035257E-3</v>
       </c>
       <c r="G13">
         <v>2015</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>94949533589880.47</v>
+        <v>94949533589880.469</v>
       </c>
       <c r="D14">
-        <v>0.01763152566237159</v>
+        <v>1.763152566237159E-2</v>
       </c>
       <c r="E14">
-        <v>97443271115215.09</v>
+        <v>97443271115215.094</v>
       </c>
       <c r="F14">
-        <v>0.01067027667490726</v>
+        <v>1.067027667490726E-2</v>
       </c>
       <c r="G14">
         <v>2016</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>738780485668018.3</v>
+        <v>738780485668018.25</v>
       </c>
       <c r="D15">
-        <v>0.003627579128238162</v>
+        <v>3.627579128238162E-3</v>
       </c>
       <c r="E15">
-        <v>656656822772716.9</v>
+        <v>656656822772716.88</v>
       </c>
       <c r="F15">
-        <v>0.002311162459456705</v>
+        <v>2.3111624594567052E-3</v>
       </c>
       <c r="G15">
         <v>2016</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>463937418975017.1</v>
+        <v>463937418975017.13</v>
       </c>
       <c r="D16">
-        <v>0.006705828770078318</v>
+        <v>6.7058287700783176E-3</v>
       </c>
       <c r="E16">
-        <v>383841301219644.4</v>
+        <v>383841301219644.38</v>
       </c>
       <c r="F16">
-        <v>0.003628317714496285</v>
+        <v>3.6283177144962849E-3</v>
       </c>
       <c r="G16">
         <v>2016</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
       </c>
       <c r="C17">
         <v>106714147699941.8</v>
       </c>
       <c r="D17">
-        <v>0.01767826972581955</v>
+        <v>1.767826972581955E-2</v>
       </c>
       <c r="E17">
         <v>106321974882725.3</v>
       </c>
       <c r="F17">
-        <v>0.01060982934596235</v>
+        <v>1.060982934596235E-2</v>
       </c>
       <c r="G17">
         <v>2017</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>743466203427861.3</v>
+        <v>743466203427861.25</v>
       </c>
       <c r="D18">
-        <v>0.003798645743078679</v>
+        <v>3.7986457430786791E-3</v>
       </c>
       <c r="E18">
         <v>662120490346396.5</v>
       </c>
       <c r="F18">
-        <v>0.002282678543272328</v>
+        <v>2.282678543272328E-3</v>
       </c>
       <c r="G18">
         <v>2017</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>10</v>
       </c>
       <c r="C19">
-        <v>466710713130434.1</v>
+        <v>466710713130434.13</v>
       </c>
       <c r="D19">
-        <v>0.005780231079888961</v>
+        <v>5.7802310798889612E-3</v>
       </c>
       <c r="E19">
-        <v>381779654547453.6</v>
+        <v>381779654547453.63</v>
       </c>
       <c r="F19">
-        <v>0.00393490402923371</v>
+        <v>3.9349040292337104E-3</v>
       </c>
       <c r="G19">
         <v>2017</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
       </c>
       <c r="C20">
         <v>102815127253097.7</v>
       </c>
       <c r="D20">
-        <v>0.01948049883064493</v>
+        <v>1.948049883064493E-2</v>
       </c>
       <c r="E20">
-        <v>103087516763583.4</v>
+        <v>103087516763583.41</v>
       </c>
       <c r="F20">
-        <v>0.01065147310815381</v>
+        <v>1.065147310815381E-2</v>
       </c>
       <c r="G20">
         <v>2018</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
       </c>
       <c r="C21">
-        <v>763539314072605.8</v>
+        <v>763539314072605.75</v>
       </c>
       <c r="D21">
-        <v>0.004209528121384252</v>
+        <v>4.2095281213842522E-3</v>
       </c>
       <c r="E21">
-        <v>673138750807045.9</v>
+        <v>673138750807045.88</v>
       </c>
       <c r="F21">
-        <v>0.002414985684717518</v>
+        <v>2.4149856847175181E-3</v>
       </c>
       <c r="G21">
         <v>2018</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>472442783022584.3</v>
+        <v>472442783022584.31</v>
       </c>
       <c r="D22">
-        <v>0.00666593969167516</v>
+        <v>6.6659396916751599E-3</v>
       </c>
       <c r="E22">
-        <v>384636497963583.4</v>
+        <v>384636497963583.38</v>
       </c>
       <c r="F22">
-        <v>0.003983354422521471</v>
+        <v>3.9833544225214707E-3</v>
       </c>
       <c r="G22">
         <v>2018</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
       </c>
       <c r="C23">
         <v>102728911228632.7</v>
       </c>
       <c r="D23">
-        <v>0.01932421596475239</v>
+        <v>1.9324215964752391E-2</v>
       </c>
       <c r="E23">
         <v>101560903390185.7</v>
       </c>
       <c r="F23">
-        <v>0.01072536819230279</v>
+        <v>1.0725368192302791E-2</v>
       </c>
       <c r="G23">
         <v>2019</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>785722684927536.6</v>
+        <v>785722684927536.63</v>
       </c>
       <c r="D24">
-        <v>0.004006708035555752</v>
+        <v>4.0067080355557522E-3</v>
       </c>
       <c r="E24">
-        <v>690724407308225.6</v>
+        <v>690724407308225.63</v>
       </c>
       <c r="F24">
-        <v>0.002246625483621461</v>
+        <v>2.2466254836214609E-3</v>
       </c>
       <c r="G24">
         <v>2019</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>470041026671510.9</v>
+        <v>470041026671510.88</v>
       </c>
       <c r="D25">
-        <v>0.006118556493487824</v>
+        <v>6.1185564934878242E-3</v>
       </c>
       <c r="E25">
-        <v>380070111133158.6</v>
+        <v>380070111133158.63</v>
       </c>
       <c r="F25">
-        <v>0.003382739854732597</v>
+        <v>3.3827398547325968E-3</v>
       </c>
       <c r="G25">
         <v>2019</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>109206175012510.6</v>
+        <v>109206175012510.59</v>
       </c>
       <c r="D26">
-        <v>0.01846478673108047</v>
+        <v>1.8464786731080471E-2</v>
       </c>
       <c r="E26">
         <v>108911586853772.8</v>
       </c>
       <c r="F26">
-        <v>0.0113766351943404</v>
+        <v>1.1376635194340399E-2</v>
       </c>
       <c r="G26">
         <v>2020</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
       </c>
       <c r="C27">
-        <v>725229953888637.8</v>
+        <v>725229953888637.75</v>
       </c>
       <c r="D27">
-        <v>0.005111209940553299</v>
+        <v>5.1112099405532987E-3</v>
       </c>
       <c r="E27">
-        <v>631707858130312.4</v>
+        <v>631707858130312.38</v>
       </c>
       <c r="F27">
-        <v>0.002904388256596372</v>
+        <v>2.9043882565963721E-3</v>
       </c>
       <c r="G27">
         <v>2020</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>542833894277224.6</v>
+        <v>542833894277224.63</v>
       </c>
       <c r="D28">
-        <v>0.007573410660767794</v>
+        <v>7.5734106607677938E-3</v>
       </c>
       <c r="E28">
-        <v>443688172064008.8</v>
+        <v>443688172064008.81</v>
       </c>
       <c r="F28">
-        <v>0.004075705783338396</v>
+        <v>4.0757057833383957E-3</v>
       </c>
       <c r="G28">
         <v>2020</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
       </c>
       <c r="C29">
         <v>115702657920216</v>
       </c>
       <c r="D29">
-        <v>0.01871513832954568</v>
+        <v>1.8715138329545682E-2</v>
       </c>
       <c r="E29">
         <v>114507305610542</v>
       </c>
       <c r="F29">
-        <v>0.01256796325551925</v>
+        <v>1.256796325551925E-2</v>
       </c>
       <c r="G29">
         <v>2021</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
       </c>
       <c r="C30">
         <v>740237887591334</v>
       </c>
       <c r="D30">
-        <v>0.005280554382790566</v>
+        <v>5.2805543827905664E-3</v>
       </c>
       <c r="E30">
-        <v>654298806890515.4</v>
+        <v>654298806890515.38</v>
       </c>
       <c r="F30">
-        <v>0.002965113385254872</v>
+        <v>2.965113385254872E-3</v>
       </c>
       <c r="G30">
         <v>2021</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>10</v>
       </c>
       <c r="C31">
-        <v>539251017041180.6</v>
+        <v>539251017041180.63</v>
       </c>
       <c r="D31">
-        <v>0.006766775110558273</v>
+        <v>6.7667751105582727E-3</v>
       </c>
       <c r="E31">
-        <v>424086692809876.8</v>
+        <v>424086692809876.81</v>
       </c>
       <c r="F31">
-        <v>0.004135398991834825</v>
+        <v>4.1353989918348254E-3</v>
       </c>
       <c r="G31">
         <v>2021</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
       </c>
       <c r="C32">
-        <v>77455779623217.56</v>
+        <v>77455779623217.563</v>
       </c>
       <c r="D32">
-        <v>0.02386802639417538</v>
+        <v>2.386802639417538E-2</v>
       </c>
       <c r="E32">
-        <v>80607472965030.16</v>
+        <v>80607472965030.156</v>
       </c>
       <c r="F32">
-        <v>0.01402492840310461</v>
+        <v>1.4024928403104609E-2</v>
       </c>
       <c r="G32">
         <v>2022</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
       </c>
       <c r="C33">
-        <v>808967665745271.6</v>
+        <v>808967665745271.63</v>
       </c>
       <c r="D33">
-        <v>0.004206329365299333</v>
+        <v>4.2063293652993333E-3</v>
       </c>
       <c r="E33">
-        <v>711111697265836.9</v>
+        <v>711111697265836.88</v>
       </c>
       <c r="F33">
-        <v>0.002241514225886723</v>
+        <v>2.241514225886723E-3</v>
       </c>
       <c r="G33">
         <v>2022</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>515292204959592.8</v>
+        <v>515292204959592.81</v>
       </c>
       <c r="D34">
-        <v>0.005754933386298816</v>
+        <v>5.7549333862988161E-3</v>
       </c>
       <c r="E34">
-        <v>408039328654243.4</v>
+        <v>408039328654243.38</v>
       </c>
       <c r="F34">
-        <v>0.003617340596444244</v>
+        <v>3.617340596444244E-3</v>
       </c>
       <c r="G34">
         <v>2022</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
       </c>
       <c r="C35">
-        <v>63771681855477.83</v>
+        <v>63771681855477.828</v>
       </c>
       <c r="D35">
-        <v>0.02306217911791301</v>
+        <v>2.3062179117913011E-2</v>
       </c>
       <c r="E35">
-        <v>65807010330965.72</v>
+        <v>65807010330965.719</v>
       </c>
       <c r="F35">
-        <v>0.01270596454839374</v>
+        <v>1.270596454839374E-2</v>
       </c>
       <c r="G35">
         <v>2023</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
       </c>
       <c r="C36">
-        <v>840870692753258.1</v>
+        <v>840870692753258.13</v>
       </c>
       <c r="D36">
-        <v>0.004195694567170382</v>
+        <v>4.1956945671703817E-3</v>
       </c>
       <c r="E36">
-        <v>737405955235394.9</v>
+        <v>737405955235394.88</v>
       </c>
       <c r="F36">
-        <v>0.002317908594125891</v>
+        <v>2.3179085941258909E-3</v>
       </c>
       <c r="G36">
         <v>2023</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>10</v>
       </c>
       <c r="C37">
-        <v>513660236727997.7</v>
+        <v>513660236727997.69</v>
       </c>
       <c r="D37">
-        <v>0.006273712721297701</v>
+        <v>6.2737127212977011E-3</v>
       </c>
       <c r="E37">
-        <v>404271449121456.9</v>
+        <v>404271449121456.88</v>
       </c>
       <c r="F37">
-        <v>0.004179111851218591</v>
+        <v>4.1791118512185914E-3</v>
       </c>
       <c r="G37">
         <v>2023</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Desocupadas</t>
-        </is>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
       </c>
       <c r="C38">
-        <v>55329755170129.27</v>
+        <v>55329755170129.273</v>
       </c>
       <c r="D38">
-        <v>0.02540710516743215</v>
+        <v>2.5407105167432151E-2</v>
       </c>
       <c r="E38">
         <v>56763191149163</v>
       </c>
       <c r="F38">
-        <v>0.0152838840970458</v>
+        <v>1.52838840970458E-2</v>
       </c>
       <c r="G38">
         <v>2024</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Dentro</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Ocupada</t>
-        </is>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>9</v>
       </c>
       <c r="C39">
-        <v>863436931401718.8</v>
+        <v>863436931401718.75</v>
       </c>
       <c r="D39">
-        <v>0.004033819389380905</v>
+        <v>4.0338193893809052E-3</v>
       </c>
       <c r="E39">
-        <v>756126590619071.4</v>
+        <v>756126590619071.38</v>
       </c>
       <c r="F39">
-        <v>0.002086770224493585</v>
+        <v>2.0867702244935851E-3</v>
       </c>
       <c r="G39">
         <v>2024</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Fora</t>
-        </is>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>10</v>
       </c>
       <c r="C40">
-        <v>511833022292887.6</v>
+        <v>511833022292887.63</v>
       </c>
       <c r="D40">
-        <v>0.006780198211146846</v>
+        <v>6.780198211146846E-3</v>
       </c>
       <c r="E40">
-        <v>402735991423626.6</v>
+        <v>402735991423626.63</v>
       </c>
       <c r="F40">
-        <v>0.003703274159391511</v>
+        <v>3.7032741593915112E-3</v>
       </c>
       <c r="G40">
         <v>2024</v>
